--- a/research/traditional_assets/database/data/estonia/estonia_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_beverage_alcoholic.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0421</v>
+        <v>0.0395</v>
       </c>
       <c r="E2">
-        <v>-0.286</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="G2">
-        <v>0.1776758409785933</v>
+        <v>0.1602564102564103</v>
       </c>
       <c r="H2">
-        <v>0.1776758409785933</v>
+        <v>0.1602564102564103</v>
       </c>
       <c r="I2">
-        <v>0.05137614678899083</v>
+        <v>0.1135897435897436</v>
       </c>
       <c r="J2">
-        <v>0.04097859327217126</v>
+        <v>0.1059645061728395</v>
       </c>
       <c r="K2">
-        <v>0.134</v>
+        <v>0.404</v>
       </c>
       <c r="L2">
-        <v>0.04097859327217126</v>
+        <v>0.1035897435897436</v>
       </c>
       <c r="M2">
-        <v>0.187</v>
+        <v>0.165</v>
       </c>
       <c r="N2">
-        <v>0.01298611111111111</v>
+        <v>0.0123134328358209</v>
       </c>
       <c r="O2">
-        <v>1.395522388059701</v>
+        <v>0.4084158415841584</v>
       </c>
       <c r="P2">
-        <v>0.187</v>
+        <v>0.165</v>
       </c>
       <c r="Q2">
-        <v>0.01298611111111111</v>
+        <v>0.0123134328358209</v>
       </c>
       <c r="R2">
-        <v>1.395522388059701</v>
+        <v>0.4084158415841584</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.6840000000000001</v>
+        <v>0.725</v>
       </c>
       <c r="V2">
-        <v>0.0475</v>
+        <v>0.0541044776119403</v>
       </c>
       <c r="W2">
-        <v>0.0325242718446602</v>
+        <v>0.09373549883990721</v>
       </c>
       <c r="X2">
-        <v>0.05549719142139366</v>
+        <v>0.09673299534091119</v>
       </c>
       <c r="Y2">
-        <v>-0.02297291957673347</v>
+        <v>-0.002997496501003977</v>
       </c>
       <c r="Z2">
-        <v>0.9802158273381294</v>
+        <v>1.075565361279647</v>
       </c>
       <c r="AA2">
-        <v>0.04016786570743405</v>
+        <v>0.1139717523646095</v>
       </c>
       <c r="AB2">
-        <v>0.05549719142139366</v>
+        <v>0.09673299534091119</v>
       </c>
       <c r="AC2">
-        <v>-0.01532932571395961</v>
+        <v>0.01723875702369833</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.6840000000000001</v>
+        <v>-0.725</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.04986876640419947</v>
+        <v>-0.05719921104536489</v>
       </c>
       <c r="AK2">
-        <v>-0.1886376172090458</v>
+        <v>-0.2187028657616893</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-1.06875</v>
+        <v>-0.8295194508009153</v>
       </c>
     </row>
     <row r="3">
@@ -716,46 +716,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0421</v>
+        <v>0.0395</v>
       </c>
       <c r="E3">
-        <v>-0.286</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="G3">
-        <v>0.1776758409785933</v>
+        <v>0.1602564102564103</v>
       </c>
       <c r="H3">
-        <v>0.1776758409785933</v>
+        <v>0.1602564102564103</v>
       </c>
       <c r="I3">
-        <v>0.05137614678899083</v>
+        <v>0.1135897435897436</v>
       </c>
       <c r="J3">
-        <v>0.04097859327217126</v>
+        <v>0.1059645061728395</v>
       </c>
       <c r="K3">
-        <v>0.134</v>
+        <v>0.404</v>
       </c>
       <c r="L3">
-        <v>0.04097859327217126</v>
+        <v>0.1035897435897436</v>
       </c>
       <c r="M3">
-        <v>0.187</v>
+        <v>0.165</v>
       </c>
       <c r="N3">
-        <v>0.01298611111111111</v>
+        <v>0.0123134328358209</v>
       </c>
       <c r="O3">
-        <v>1.395522388059701</v>
+        <v>0.4084158415841584</v>
       </c>
       <c r="P3">
-        <v>0.187</v>
+        <v>0.165</v>
       </c>
       <c r="Q3">
-        <v>0.01298611111111111</v>
+        <v>0.0123134328358209</v>
       </c>
       <c r="R3">
-        <v>1.395522388059701</v>
+        <v>0.4084158415841584</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,31 +764,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.6840000000000001</v>
+        <v>0.725</v>
       </c>
       <c r="V3">
-        <v>0.0475</v>
+        <v>0.0541044776119403</v>
       </c>
       <c r="W3">
-        <v>0.0325242718446602</v>
+        <v>0.09373549883990721</v>
       </c>
       <c r="X3">
-        <v>0.05549719142139366</v>
+        <v>0.09673299534091119</v>
       </c>
       <c r="Y3">
-        <v>-0.02297291957673347</v>
+        <v>-0.002997496501003977</v>
       </c>
       <c r="Z3">
-        <v>0.9802158273381294</v>
+        <v>1.075565361279647</v>
       </c>
       <c r="AA3">
-        <v>0.04016786570743405</v>
+        <v>0.1139717523646095</v>
       </c>
       <c r="AB3">
-        <v>0.05549719142139366</v>
+        <v>0.09673299534091119</v>
       </c>
       <c r="AC3">
-        <v>-0.01532932571395961</v>
+        <v>0.01723875702369833</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.6840000000000001</v>
+        <v>-0.725</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.04986876640419947</v>
+        <v>-0.05719921104536489</v>
       </c>
       <c r="AK3">
-        <v>-0.1886376172090458</v>
+        <v>-0.2187028657616893</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-1.06875</v>
+        <v>-0.8295194508009153</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/estonia/estonia_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_beverage_alcoholic.xlsx
@@ -588,46 +588,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0395</v>
-      </c>
-      <c r="E2">
-        <v>-0.06469999999999999</v>
+        <v>0.07919999999999999</v>
       </c>
       <c r="G2">
-        <v>0.1602564102564103</v>
+        <v>0.2351351351351351</v>
       </c>
       <c r="H2">
-        <v>0.1602564102564103</v>
+        <v>0.2351351351351351</v>
       </c>
       <c r="I2">
-        <v>0.1135897435897436</v>
+        <v>-0.008708708708708709</v>
       </c>
       <c r="J2">
-        <v>0.1059645061728395</v>
+        <v>-0.008708708708708709</v>
       </c>
       <c r="K2">
-        <v>0.404</v>
+        <v>-0.057</v>
       </c>
       <c r="L2">
-        <v>0.1035897435897436</v>
+        <v>-0.01711711711711712</v>
       </c>
       <c r="M2">
-        <v>0.165</v>
+        <v>0.172</v>
       </c>
       <c r="N2">
-        <v>0.0123134328358209</v>
+        <v>0.0147008547008547</v>
       </c>
       <c r="O2">
-        <v>0.4084158415841584</v>
+        <v>-3.017543859649122</v>
       </c>
       <c r="P2">
-        <v>0.165</v>
+        <v>0.172</v>
       </c>
       <c r="Q2">
-        <v>0.0123134328358209</v>
+        <v>0.0147008547008547</v>
       </c>
       <c r="R2">
-        <v>0.4084158415841584</v>
+        <v>-3.017543859649122</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,67 +633,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.725</v>
+        <v>0.348</v>
       </c>
       <c r="V2">
-        <v>0.0541044776119403</v>
+        <v>0.02974358974358974</v>
       </c>
       <c r="W2">
-        <v>0.09373549883990721</v>
+        <v>-0.01410891089108911</v>
       </c>
       <c r="X2">
-        <v>0.09673299534091119</v>
+        <v>0.07785357384959046</v>
       </c>
       <c r="Y2">
-        <v>-0.002997496501003977</v>
+        <v>-0.09196248474067957</v>
       </c>
       <c r="Z2">
-        <v>1.075565361279647</v>
+        <v>1.004524886877828</v>
       </c>
       <c r="AA2">
-        <v>0.1139717523646095</v>
+        <v>-0.008748114630467572</v>
       </c>
       <c r="AB2">
-        <v>0.09673299534091119</v>
+        <v>0.07772819731086632</v>
       </c>
       <c r="AC2">
-        <v>0.01723875702369833</v>
+        <v>-0.08647631194133389</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="AG2">
-        <v>-0.725</v>
+        <v>-0.297</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.004340056165432729</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.01265194740759117</v>
       </c>
       <c r="AJ2">
-        <v>-0.05719921104536489</v>
+        <v>-0.0260457774269929</v>
       </c>
       <c r="AK2">
-        <v>-0.2187028657616893</v>
+        <v>-0.08064078197121911</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>0.1291139240506329</v>
       </c>
       <c r="AP2">
-        <v>-0.8295194508009153</v>
+        <v>-0.7518987341772151</v>
+      </c>
+      <c r="AQ2">
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -716,46 +716,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0395</v>
-      </c>
-      <c r="E3">
-        <v>-0.06469999999999999</v>
+        <v>0.07919999999999999</v>
       </c>
       <c r="G3">
-        <v>0.1602564102564103</v>
+        <v>0.2351351351351351</v>
       </c>
       <c r="H3">
-        <v>0.1602564102564103</v>
+        <v>0.2351351351351351</v>
       </c>
       <c r="I3">
-        <v>0.1135897435897436</v>
+        <v>-0.008708708708708709</v>
       </c>
       <c r="J3">
-        <v>0.1059645061728395</v>
+        <v>-0.008708708708708709</v>
       </c>
       <c r="K3">
-        <v>0.404</v>
+        <v>-0.057</v>
       </c>
       <c r="L3">
-        <v>0.1035897435897436</v>
+        <v>-0.01711711711711712</v>
       </c>
       <c r="M3">
-        <v>0.165</v>
+        <v>0.172</v>
       </c>
       <c r="N3">
-        <v>0.0123134328358209</v>
+        <v>0.0147008547008547</v>
       </c>
       <c r="O3">
-        <v>0.4084158415841584</v>
+        <v>-3.017543859649122</v>
       </c>
       <c r="P3">
-        <v>0.165</v>
+        <v>0.172</v>
       </c>
       <c r="Q3">
-        <v>0.0123134328358209</v>
+        <v>0.0147008547008547</v>
       </c>
       <c r="R3">
-        <v>0.4084158415841584</v>
+        <v>-3.017543859649122</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,67 +761,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.725</v>
+        <v>0.348</v>
       </c>
       <c r="V3">
-        <v>0.0541044776119403</v>
+        <v>0.02974358974358974</v>
       </c>
       <c r="W3">
-        <v>0.09373549883990721</v>
+        <v>-0.01410891089108911</v>
       </c>
       <c r="X3">
-        <v>0.09673299534091119</v>
+        <v>0.07785357384959046</v>
       </c>
       <c r="Y3">
-        <v>-0.002997496501003977</v>
+        <v>-0.09196248474067957</v>
       </c>
       <c r="Z3">
-        <v>1.075565361279647</v>
+        <v>1.004524886877828</v>
       </c>
       <c r="AA3">
-        <v>0.1139717523646095</v>
+        <v>-0.008748114630467572</v>
       </c>
       <c r="AB3">
-        <v>0.09673299534091119</v>
+        <v>0.07772819731086632</v>
       </c>
       <c r="AC3">
-        <v>0.01723875702369833</v>
+        <v>-0.08647631194133389</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="AG3">
-        <v>-0.725</v>
+        <v>-0.297</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.004340056165432729</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.01265194740759117</v>
       </c>
       <c r="AJ3">
-        <v>-0.05719921104536489</v>
+        <v>-0.0260457774269929</v>
       </c>
       <c r="AK3">
-        <v>-0.2187028657616893</v>
+        <v>-0.08064078197121911</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.1291139240506329</v>
       </c>
       <c r="AP3">
-        <v>-0.8295194508009153</v>
+        <v>-0.7518987341772151</v>
+      </c>
+      <c r="AQ3">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
